--- a/servers/maze_main_server_dev/conf.d/data/maze_answer_mechanism_v8【答题机关词库】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_answer_mechanism_v8【答题机关词库】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F5EFA46-6AF4-4DCF-8367-78ED278E6001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8E98C8C-D966-4648-9019-10E3D7972BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_answer_mechanism_v8" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="934" uniqueCount="831">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="929" uniqueCount="826">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1026,18 +1026,6 @@
     <t>我们通常用什么单位来衡量电流强度？</t>
   </si>
   <si>
-    <t>伏特 (V)</t>
-  </si>
-  <si>
-    <t>欧姆 (Ω)</t>
-  </si>
-  <si>
-    <t>安培 (A)</t>
-  </si>
-  <si>
-    <t>瓦特 (W)</t>
-  </si>
-  <si>
     <t>人体最大的器官是什么？</t>
   </si>
   <si>
@@ -1353,18 +1341,6 @@
     <t>人的正常体温大约是多少摄氏度？</t>
   </si>
   <si>
-    <t>35℃</t>
-  </si>
-  <si>
-    <t>37℃</t>
-  </si>
-  <si>
-    <t>39℃</t>
-  </si>
-  <si>
-    <t>41℃</t>
-  </si>
-  <si>
     <t>“SOS”是国际通用的什么信号？</t>
   </si>
   <si>
@@ -1542,9 +1518,6 @@
     <t>葡萄牙语</t>
   </si>
   <si>
-    <t>“白金汉宫”是哪个国家君主的 официальный官邸？</t>
-  </si>
-  <si>
     <t>世界上最干旱的沙漠是？</t>
   </si>
   <si>
@@ -1960,21 +1933,6 @@
   </si>
   <si>
     <t>X型</t>
-  </si>
-  <si>
-    <t>温度计上“℃”代表什么温标？</t>
-  </si>
-  <si>
-    <t>华氏温标</t>
-  </si>
-  <si>
-    <t>摄氏温标</t>
-  </si>
-  <si>
-    <t>开氏温标</t>
-  </si>
-  <si>
-    <t>列氏温标</t>
   </si>
   <si>
     <t>蜜蜂通过跳舞来传递什么信息？</t>
@@ -2544,6 +2502,42 @@
   </si>
   <si>
     <t>question_bank_id</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>伏特</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>欧姆</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>安培</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>瓦特</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>35度</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>37度</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>39度</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>41度</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>“白金汉宫”是哪个国家君主的官邸？</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -2971,7 +2965,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:H189"/>
+  <dimension ref="A1:H188"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" style="8" bestFit="1" customWidth="1"/>
@@ -2999,7 +2993,7 @@
     </row>
     <row r="2" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A2" s="6" t="s">
-        <v>829</v>
+        <v>815</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>6</v>
@@ -3028,7 +3022,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>830</v>
+        <v>816</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>7</v>
@@ -3424,7 +3418,7 @@
         <v>77</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>828</v>
+        <v>814</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>78</v>
@@ -4958,16 +4952,16 @@
         <v>324</v>
       </c>
       <c r="D77" s="7" t="s">
-        <v>325</v>
+        <v>817</v>
       </c>
       <c r="E77" s="7" t="s">
-        <v>326</v>
+        <v>818</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>327</v>
+        <v>819</v>
       </c>
       <c r="G77" s="7" t="s">
-        <v>328</v>
+        <v>820</v>
       </c>
       <c r="H77" s="7">
         <v>3</v>
@@ -4981,19 +4975,19 @@
         <v>1</v>
       </c>
       <c r="C78" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="D78" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="E78" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="F78" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="G78" s="7" t="s">
         <v>329</v>
-      </c>
-      <c r="D78" s="7" t="s">
-        <v>330</v>
-      </c>
-      <c r="E78" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="F78" s="7" t="s">
-        <v>332</v>
-      </c>
-      <c r="G78" s="7" t="s">
-        <v>333</v>
       </c>
       <c r="H78" s="7">
         <v>4</v>
@@ -5007,19 +5001,19 @@
         <v>1</v>
       </c>
       <c r="C79" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="D79" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="E79" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="F79" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="G79" s="7" t="s">
         <v>334</v>
-      </c>
-      <c r="D79" s="7" t="s">
-        <v>335</v>
-      </c>
-      <c r="E79" s="7" t="s">
-        <v>336</v>
-      </c>
-      <c r="F79" s="7" t="s">
-        <v>337</v>
-      </c>
-      <c r="G79" s="7" t="s">
-        <v>338</v>
       </c>
       <c r="H79" s="7">
         <v>2</v>
@@ -5033,19 +5027,19 @@
         <v>1</v>
       </c>
       <c r="C80" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="D80" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="E80" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="F80" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="G80" s="7" t="s">
         <v>339</v>
-      </c>
-      <c r="D80" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="E80" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="F80" s="7" t="s">
-        <v>342</v>
-      </c>
-      <c r="G80" s="7" t="s">
-        <v>343</v>
       </c>
       <c r="H80" s="7">
         <v>1</v>
@@ -5059,19 +5053,19 @@
         <v>1</v>
       </c>
       <c r="C81" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="D81" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="E81" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="F81" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="G81" s="7" t="s">
         <v>344</v>
-      </c>
-      <c r="D81" s="7" t="s">
-        <v>345</v>
-      </c>
-      <c r="E81" s="7" t="s">
-        <v>346</v>
-      </c>
-      <c r="F81" s="7" t="s">
-        <v>347</v>
-      </c>
-      <c r="G81" s="7" t="s">
-        <v>348</v>
       </c>
       <c r="H81" s="7">
         <v>3</v>
@@ -5085,19 +5079,19 @@
         <v>1</v>
       </c>
       <c r="C82" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="D82" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="E82" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="F82" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="G82" s="7" t="s">
         <v>349</v>
-      </c>
-      <c r="D82" s="7" t="s">
-        <v>350</v>
-      </c>
-      <c r="E82" s="7" t="s">
-        <v>351</v>
-      </c>
-      <c r="F82" s="7" t="s">
-        <v>352</v>
-      </c>
-      <c r="G82" s="7" t="s">
-        <v>353</v>
       </c>
       <c r="H82" s="7">
         <v>4</v>
@@ -5111,19 +5105,19 @@
         <v>1</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="D83" s="7" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="E83" s="7" t="s">
         <v>151</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="G83" s="7" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="H83" s="7">
         <v>2</v>
@@ -5137,19 +5131,19 @@
         <v>1</v>
       </c>
       <c r="C84" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="D84" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="E84" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="F84" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="G84" s="7" t="s">
         <v>358</v>
-      </c>
-      <c r="D84" s="7" t="s">
-        <v>359</v>
-      </c>
-      <c r="E84" s="7" t="s">
-        <v>360</v>
-      </c>
-      <c r="F84" s="7" t="s">
-        <v>361</v>
-      </c>
-      <c r="G84" s="7" t="s">
-        <v>362</v>
       </c>
       <c r="H84" s="7">
         <v>2</v>
@@ -5163,19 +5157,19 @@
         <v>1</v>
       </c>
       <c r="C85" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="D85" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="E85" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="F85" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="G85" s="7" t="s">
         <v>363</v>
-      </c>
-      <c r="D85" s="7" t="s">
-        <v>364</v>
-      </c>
-      <c r="E85" s="7" t="s">
-        <v>365</v>
-      </c>
-      <c r="F85" s="7" t="s">
-        <v>366</v>
-      </c>
-      <c r="G85" s="7" t="s">
-        <v>367</v>
       </c>
       <c r="H85" s="7">
         <v>2</v>
@@ -5189,19 +5183,19 @@
         <v>1</v>
       </c>
       <c r="C86" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="D86" s="7" t="s">
+        <v>365</v>
+      </c>
+      <c r="E86" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="F86" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="G86" s="7" t="s">
         <v>368</v>
-      </c>
-      <c r="D86" s="7" t="s">
-        <v>369</v>
-      </c>
-      <c r="E86" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="F86" s="7" t="s">
-        <v>371</v>
-      </c>
-      <c r="G86" s="7" t="s">
-        <v>372</v>
       </c>
       <c r="H86" s="7">
         <v>1</v>
@@ -5215,10 +5209,10 @@
         <v>1</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="D87" s="7" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="E87" s="7" t="s">
         <v>84</v>
@@ -5241,19 +5235,19 @@
         <v>1</v>
       </c>
       <c r="C88" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="D88" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="E88" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="F88" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="G88" s="7" t="s">
         <v>375</v>
-      </c>
-      <c r="D88" s="7" t="s">
-        <v>376</v>
-      </c>
-      <c r="E88" s="7" t="s">
-        <v>377</v>
-      </c>
-      <c r="F88" s="7" t="s">
-        <v>378</v>
-      </c>
-      <c r="G88" s="7" t="s">
-        <v>379</v>
       </c>
       <c r="H88" s="7">
         <v>3</v>
@@ -5267,19 +5261,19 @@
         <v>1</v>
       </c>
       <c r="C89" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="D89" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="E89" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="F89" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="G89" s="7" t="s">
         <v>380</v>
-      </c>
-      <c r="D89" s="7" t="s">
-        <v>381</v>
-      </c>
-      <c r="E89" s="7" t="s">
-        <v>382</v>
-      </c>
-      <c r="F89" s="7" t="s">
-        <v>383</v>
-      </c>
-      <c r="G89" s="7" t="s">
-        <v>384</v>
       </c>
       <c r="H89" s="7">
         <v>1</v>
@@ -5293,10 +5287,10 @@
         <v>1</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="D90" s="7" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="E90" s="7" t="s">
         <v>82</v>
@@ -5319,19 +5313,19 @@
         <v>1</v>
       </c>
       <c r="C91" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="D91" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="E91" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="F91" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="G91" s="7" t="s">
         <v>387</v>
-      </c>
-      <c r="D91" s="7" t="s">
-        <v>388</v>
-      </c>
-      <c r="E91" s="7" t="s">
-        <v>389</v>
-      </c>
-      <c r="F91" s="7" t="s">
-        <v>390</v>
-      </c>
-      <c r="G91" s="7" t="s">
-        <v>391</v>
       </c>
       <c r="H91" s="7">
         <v>2</v>
@@ -5345,19 +5339,19 @@
         <v>1</v>
       </c>
       <c r="C92" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="D92" s="7" t="s">
+        <v>389</v>
+      </c>
+      <c r="E92" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="F92" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="G92" s="7" t="s">
         <v>392</v>
-      </c>
-      <c r="D92" s="7" t="s">
-        <v>393</v>
-      </c>
-      <c r="E92" s="7" t="s">
-        <v>394</v>
-      </c>
-      <c r="F92" s="7" t="s">
-        <v>395</v>
-      </c>
-      <c r="G92" s="7" t="s">
-        <v>396</v>
       </c>
       <c r="H92" s="7">
         <v>2</v>
@@ -5371,7 +5365,7 @@
         <v>1</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="D93" s="7" t="s">
         <v>158</v>
@@ -5397,19 +5391,19 @@
         <v>2</v>
       </c>
       <c r="C94" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="D94" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="E94" s="7" t="s">
+        <v>396</v>
+      </c>
+      <c r="F94" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="G94" s="7" t="s">
         <v>398</v>
-      </c>
-      <c r="D94" s="7" t="s">
-        <v>399</v>
-      </c>
-      <c r="E94" s="7" t="s">
-        <v>400</v>
-      </c>
-      <c r="F94" s="7" t="s">
-        <v>401</v>
-      </c>
-      <c r="G94" s="7" t="s">
-        <v>402</v>
       </c>
       <c r="H94" s="7">
         <v>2</v>
@@ -5423,19 +5417,19 @@
         <v>2</v>
       </c>
       <c r="C95" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="D95" s="7" t="s">
+        <v>400</v>
+      </c>
+      <c r="E95" s="7" t="s">
+        <v>401</v>
+      </c>
+      <c r="F95" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="G95" s="7" t="s">
         <v>403</v>
-      </c>
-      <c r="D95" s="7" t="s">
-        <v>404</v>
-      </c>
-      <c r="E95" s="7" t="s">
-        <v>405</v>
-      </c>
-      <c r="F95" s="7" t="s">
-        <v>406</v>
-      </c>
-      <c r="G95" s="7" t="s">
-        <v>407</v>
       </c>
       <c r="H95" s="7">
         <v>2</v>
@@ -5449,19 +5443,19 @@
         <v>2</v>
       </c>
       <c r="C96" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="D96" s="7" t="s">
+        <v>405</v>
+      </c>
+      <c r="E96" s="7" t="s">
+        <v>406</v>
+      </c>
+      <c r="F96" s="7" t="s">
+        <v>407</v>
+      </c>
+      <c r="G96" s="7" t="s">
         <v>408</v>
-      </c>
-      <c r="D96" s="7" t="s">
-        <v>409</v>
-      </c>
-      <c r="E96" s="7" t="s">
-        <v>410</v>
-      </c>
-      <c r="F96" s="7" t="s">
-        <v>411</v>
-      </c>
-      <c r="G96" s="7" t="s">
-        <v>412</v>
       </c>
       <c r="H96" s="7">
         <v>3</v>
@@ -5475,19 +5469,19 @@
         <v>2</v>
       </c>
       <c r="C97" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="D97" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="E97" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="F97" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="G97" s="7" t="s">
         <v>413</v>
-      </c>
-      <c r="D97" s="7" t="s">
-        <v>414</v>
-      </c>
-      <c r="E97" s="7" t="s">
-        <v>415</v>
-      </c>
-      <c r="F97" s="7" t="s">
-        <v>416</v>
-      </c>
-      <c r="G97" s="7" t="s">
-        <v>417</v>
       </c>
       <c r="H97" s="7">
         <v>3</v>
@@ -5501,19 +5495,19 @@
         <v>2</v>
       </c>
       <c r="C98" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="D98" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="E98" s="7" t="s">
+        <v>416</v>
+      </c>
+      <c r="F98" s="7" t="s">
+        <v>417</v>
+      </c>
+      <c r="G98" s="7" t="s">
         <v>418</v>
-      </c>
-      <c r="D98" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="E98" s="7" t="s">
-        <v>420</v>
-      </c>
-      <c r="F98" s="7" t="s">
-        <v>421</v>
-      </c>
-      <c r="G98" s="7" t="s">
-        <v>422</v>
       </c>
       <c r="H98" s="7">
         <v>3</v>
@@ -5527,19 +5521,19 @@
         <v>2</v>
       </c>
       <c r="C99" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="D99" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="E99" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="F99" s="7" t="s">
+        <v>422</v>
+      </c>
+      <c r="G99" s="7" t="s">
         <v>423</v>
-      </c>
-      <c r="D99" s="7" t="s">
-        <v>424</v>
-      </c>
-      <c r="E99" s="7" t="s">
-        <v>425</v>
-      </c>
-      <c r="F99" s="7" t="s">
-        <v>426</v>
-      </c>
-      <c r="G99" s="7" t="s">
-        <v>427</v>
       </c>
       <c r="H99" s="7">
         <v>3</v>
@@ -5553,19 +5547,19 @@
         <v>2</v>
       </c>
       <c r="C100" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="D100" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="E100" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="F100" s="7" t="s">
+        <v>427</v>
+      </c>
+      <c r="G100" s="7" t="s">
         <v>428</v>
-      </c>
-      <c r="D100" s="7" t="s">
-        <v>429</v>
-      </c>
-      <c r="E100" s="7" t="s">
-        <v>430</v>
-      </c>
-      <c r="F100" s="7" t="s">
-        <v>431</v>
-      </c>
-      <c r="G100" s="7" t="s">
-        <v>432</v>
       </c>
       <c r="H100" s="7">
         <v>3</v>
@@ -5579,19 +5573,19 @@
         <v>2</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="D101" s="7" t="s">
-        <v>434</v>
+        <v>821</v>
       </c>
       <c r="E101" s="7" t="s">
-        <v>435</v>
+        <v>822</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>436</v>
+        <v>823</v>
       </c>
       <c r="G101" s="7" t="s">
-        <v>437</v>
+        <v>824</v>
       </c>
       <c r="H101" s="7">
         <v>2</v>
@@ -5605,19 +5599,19 @@
         <v>2</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="D102" s="7" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="E102" s="7" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="F102" s="7" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="G102" s="7" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="H102" s="7">
         <v>2</v>
@@ -5631,19 +5625,19 @@
         <v>2</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="D103" s="7" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="E103" s="7" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="G103" s="7" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="H103" s="7">
         <v>4</v>
@@ -5657,19 +5651,19 @@
         <v>2</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="D104" s="7" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="E104" s="7" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="F104" s="7" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="G104" s="7" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="H104" s="7">
         <v>2</v>
@@ -5683,7 +5677,7 @@
         <v>2</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="D105" s="7" t="s">
         <v>20</v>
@@ -5709,19 +5703,19 @@
         <v>2</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="D106" s="7" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="E106" s="7" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="F106" s="7" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
       <c r="G106" s="7" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="H106" s="7">
         <v>2</v>
@@ -5735,7 +5729,7 @@
         <v>2</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="D107" s="7" t="s">
         <v>45</v>
@@ -5747,7 +5741,7 @@
         <v>46</v>
       </c>
       <c r="G107" s="7" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="H107" s="7">
         <v>2</v>
@@ -5761,16 +5755,16 @@
         <v>2</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="D108" s="7" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="E108" s="7" t="s">
         <v>266</v>
       </c>
       <c r="F108" s="7" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="G108" s="7" t="s">
         <v>83</v>
@@ -5787,19 +5781,19 @@
         <v>2</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="D109" s="7" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="E109" s="7" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="F109" s="7" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="G109" s="7" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="H109" s="7">
         <v>2</v>
@@ -5813,19 +5807,19 @@
         <v>2</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="D110" s="7" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="E110" s="7" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="F110" s="7" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="G110" s="7" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="H110" s="7">
         <v>3</v>
@@ -5839,19 +5833,19 @@
         <v>2</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="D111" s="7" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="E111" s="7" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="F111" s="7" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="G111" s="7" t="s">
-        <v>478</v>
+        <v>470</v>
       </c>
       <c r="H111" s="7">
         <v>2</v>
@@ -5865,16 +5859,16 @@
         <v>2</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="D112" s="7" t="s">
         <v>56</v>
       </c>
       <c r="E112" s="7" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="F112" s="7" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="G112" s="7" t="s">
         <v>55</v>
@@ -5891,19 +5885,19 @@
         <v>2</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="D113" s="7" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="E113" s="7" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="F113" s="7" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="G113" s="7" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="H113" s="7">
         <v>1</v>
@@ -5917,19 +5911,19 @@
         <v>2</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="D114" s="7" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="E114" s="7" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="F114" s="7" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="G114" s="7" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="H114" s="7">
         <v>1</v>
@@ -5943,19 +5937,19 @@
         <v>2</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="D115" s="7" t="s">
-        <v>493</v>
+        <v>485</v>
       </c>
       <c r="E115" s="7" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="F115" s="7" t="s">
-        <v>495</v>
+        <v>487</v>
       </c>
       <c r="G115" s="7" t="s">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="H115" s="7">
         <v>4</v>
@@ -5969,7 +5963,7 @@
         <v>2</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>497</v>
+        <v>825</v>
       </c>
       <c r="D116" s="7" t="s">
         <v>82</v>
@@ -5995,19 +5989,19 @@
         <v>2</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>498</v>
+        <v>489</v>
       </c>
       <c r="D117" s="7" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="E117" s="7" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="F117" s="7" t="s">
-        <v>500</v>
+        <v>491</v>
       </c>
       <c r="G117" s="7" t="s">
-        <v>501</v>
+        <v>492</v>
       </c>
       <c r="H117" s="7">
         <v>3</v>
@@ -6021,19 +6015,19 @@
         <v>2</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="D118" s="7" t="s">
-        <v>503</v>
+        <v>494</v>
       </c>
       <c r="E118" s="7" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="F118" s="7" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="G118" s="7" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
       <c r="H118" s="7">
         <v>2</v>
@@ -6047,13 +6041,13 @@
         <v>2</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="D119" s="7" t="s">
         <v>27</v>
       </c>
       <c r="E119" s="7" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="F119" s="7" t="s">
         <v>231</v>
@@ -6073,19 +6067,19 @@
         <v>2</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>508</v>
+        <v>499</v>
       </c>
       <c r="D120" s="7" t="s">
-        <v>509</v>
+        <v>500</v>
       </c>
       <c r="E120" s="7" t="s">
-        <v>510</v>
+        <v>501</v>
       </c>
       <c r="F120" s="7" t="s">
-        <v>511</v>
+        <v>502</v>
       </c>
       <c r="G120" s="7" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="H120" s="7">
         <v>3</v>
@@ -6099,16 +6093,16 @@
         <v>2</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="D121" s="7" t="s">
         <v>19</v>
       </c>
       <c r="E121" s="7" t="s">
-        <v>514</v>
+        <v>505</v>
       </c>
       <c r="F121" s="7" t="s">
-        <v>515</v>
+        <v>506</v>
       </c>
       <c r="G121" s="7" t="s">
         <v>59</v>
@@ -6125,19 +6119,19 @@
         <v>2</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>516</v>
+        <v>507</v>
       </c>
       <c r="D122" s="7" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="E122" s="7" t="s">
-        <v>518</v>
+        <v>509</v>
       </c>
       <c r="F122" s="7" t="s">
         <v>298</v>
       </c>
       <c r="G122" s="7" t="s">
-        <v>519</v>
+        <v>510</v>
       </c>
       <c r="H122" s="7">
         <v>3</v>
@@ -6151,19 +6145,19 @@
         <v>2</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>520</v>
+        <v>511</v>
       </c>
       <c r="D123" s="7" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="E123" s="7" t="s">
-        <v>522</v>
+        <v>513</v>
       </c>
       <c r="F123" s="7" t="s">
-        <v>523</v>
+        <v>514</v>
       </c>
       <c r="G123" s="7" t="s">
-        <v>524</v>
+        <v>515</v>
       </c>
       <c r="H123" s="7">
         <v>2</v>
@@ -6177,19 +6171,19 @@
         <v>2</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>525</v>
+        <v>516</v>
       </c>
       <c r="D124" s="7" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="E124" s="7" t="s">
-        <v>527</v>
+        <v>518</v>
       </c>
       <c r="F124" s="7" t="s">
-        <v>528</v>
+        <v>519</v>
       </c>
       <c r="G124" s="7" t="s">
-        <v>529</v>
+        <v>520</v>
       </c>
       <c r="H124" s="7">
         <v>2</v>
@@ -6203,19 +6197,19 @@
         <v>2</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>530</v>
+        <v>521</v>
       </c>
       <c r="D125" s="7" t="s">
-        <v>531</v>
+        <v>522</v>
       </c>
       <c r="E125" s="7" t="s">
-        <v>532</v>
+        <v>523</v>
       </c>
       <c r="F125" s="7" t="s">
-        <v>533</v>
+        <v>524</v>
       </c>
       <c r="G125" s="7" t="s">
-        <v>534</v>
+        <v>525</v>
       </c>
       <c r="H125" s="7">
         <v>1</v>
@@ -6229,19 +6223,19 @@
         <v>2</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>535</v>
+        <v>526</v>
       </c>
       <c r="D126" s="7" t="s">
-        <v>536</v>
+        <v>527</v>
       </c>
       <c r="E126" s="7" t="s">
-        <v>537</v>
+        <v>528</v>
       </c>
       <c r="F126" s="7" t="s">
-        <v>538</v>
+        <v>529</v>
       </c>
       <c r="G126" s="7" t="s">
-        <v>539</v>
+        <v>530</v>
       </c>
       <c r="H126" s="7">
         <v>3</v>
@@ -6255,19 +6249,19 @@
         <v>2</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>540</v>
+        <v>531</v>
       </c>
       <c r="D127" s="7" t="s">
-        <v>541</v>
+        <v>532</v>
       </c>
       <c r="E127" s="7" t="s">
-        <v>542</v>
+        <v>533</v>
       </c>
       <c r="F127" s="7" t="s">
-        <v>543</v>
+        <v>534</v>
       </c>
       <c r="G127" s="7" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="H127" s="7">
         <v>3</v>
@@ -6281,10 +6275,10 @@
         <v>2</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>545</v>
+        <v>536</v>
       </c>
       <c r="D128" s="7" t="s">
-        <v>546</v>
+        <v>537</v>
       </c>
       <c r="E128" s="7" t="s">
         <v>87</v>
@@ -6293,7 +6287,7 @@
         <v>88</v>
       </c>
       <c r="G128" s="7" t="s">
-        <v>547</v>
+        <v>538</v>
       </c>
       <c r="H128" s="7">
         <v>2</v>
@@ -6307,19 +6301,19 @@
         <v>2</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>548</v>
+        <v>539</v>
       </c>
       <c r="D129" s="7" t="s">
-        <v>549</v>
+        <v>540</v>
       </c>
       <c r="E129" s="7" t="s">
-        <v>550</v>
+        <v>541</v>
       </c>
       <c r="F129" s="7" t="s">
-        <v>551</v>
+        <v>542</v>
       </c>
       <c r="G129" s="7" t="s">
-        <v>552</v>
+        <v>543</v>
       </c>
       <c r="H129" s="7">
         <v>2</v>
@@ -6333,19 +6327,19 @@
         <v>2</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>553</v>
+        <v>544</v>
       </c>
       <c r="D130" s="7" t="s">
-        <v>554</v>
+        <v>545</v>
       </c>
       <c r="E130" s="7" t="s">
-        <v>555</v>
+        <v>546</v>
       </c>
       <c r="F130" s="7" t="s">
-        <v>556</v>
+        <v>547</v>
       </c>
       <c r="G130" s="7" t="s">
-        <v>557</v>
+        <v>548</v>
       </c>
       <c r="H130" s="7">
         <v>3</v>
@@ -6359,19 +6353,19 @@
         <v>2</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>558</v>
+        <v>549</v>
       </c>
       <c r="D131" s="7" t="s">
-        <v>559</v>
+        <v>550</v>
       </c>
       <c r="E131" s="7" t="s">
-        <v>560</v>
+        <v>551</v>
       </c>
       <c r="F131" s="7" t="s">
-        <v>561</v>
+        <v>552</v>
       </c>
       <c r="G131" s="7" t="s">
-        <v>562</v>
+        <v>553</v>
       </c>
       <c r="H131" s="7">
         <v>2</v>
@@ -6385,19 +6379,19 @@
         <v>2</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>563</v>
+        <v>554</v>
       </c>
       <c r="D132" s="7" t="s">
-        <v>564</v>
+        <v>555</v>
       </c>
       <c r="E132" s="7" t="s">
-        <v>510</v>
+        <v>501</v>
       </c>
       <c r="F132" s="7" t="s">
-        <v>565</v>
+        <v>556</v>
       </c>
       <c r="G132" s="7" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
       <c r="H132" s="7">
         <v>2</v>
@@ -6411,19 +6405,19 @@
         <v>2</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>567</v>
+        <v>558</v>
       </c>
       <c r="D133" s="7" t="s">
-        <v>568</v>
+        <v>559</v>
       </c>
       <c r="E133" s="7" t="s">
-        <v>569</v>
+        <v>560</v>
       </c>
       <c r="F133" s="7" t="s">
-        <v>570</v>
+        <v>561</v>
       </c>
       <c r="G133" s="7" t="s">
-        <v>571</v>
+        <v>562</v>
       </c>
       <c r="H133" s="7">
         <v>2</v>
@@ -6437,19 +6431,19 @@
         <v>2</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>572</v>
+        <v>563</v>
       </c>
       <c r="D134" s="7" t="s">
-        <v>573</v>
+        <v>564</v>
       </c>
       <c r="E134" s="7" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="F134" s="7" t="s">
-        <v>575</v>
+        <v>566</v>
       </c>
       <c r="G134" s="7" t="s">
-        <v>576</v>
+        <v>567</v>
       </c>
       <c r="H134" s="7">
         <v>2</v>
@@ -6463,19 +6457,19 @@
         <v>2</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>577</v>
+        <v>568</v>
       </c>
       <c r="D135" s="7" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
       <c r="E135" s="7" t="s">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="F135" s="7" t="s">
-        <v>580</v>
+        <v>571</v>
       </c>
       <c r="G135" s="7" t="s">
-        <v>581</v>
+        <v>572</v>
       </c>
       <c r="H135" s="7">
         <v>2</v>
@@ -6489,19 +6483,19 @@
         <v>2</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="D136" s="7" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="E136" s="7" t="s">
-        <v>583</v>
+        <v>574</v>
       </c>
       <c r="F136" s="7" t="s">
-        <v>584</v>
+        <v>575</v>
       </c>
       <c r="G136" s="7" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="H136" s="7">
         <v>2</v>
@@ -6515,19 +6509,19 @@
         <v>2</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>586</v>
+        <v>577</v>
       </c>
       <c r="D137" s="7" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="E137" s="7" t="s">
-        <v>588</v>
+        <v>579</v>
       </c>
       <c r="F137" s="7" t="s">
-        <v>589</v>
+        <v>580</v>
       </c>
       <c r="G137" s="7" t="s">
-        <v>590</v>
+        <v>581</v>
       </c>
       <c r="H137" s="7">
         <v>3</v>
@@ -6541,19 +6535,19 @@
         <v>2</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>591</v>
+        <v>582</v>
       </c>
       <c r="D138" s="7" t="s">
-        <v>592</v>
+        <v>583</v>
       </c>
       <c r="E138" s="7" t="s">
-        <v>593</v>
+        <v>584</v>
       </c>
       <c r="F138" s="7" t="s">
-        <v>594</v>
+        <v>585</v>
       </c>
       <c r="G138" s="7" t="s">
-        <v>595</v>
+        <v>586</v>
       </c>
       <c r="H138" s="7">
         <v>4</v>
@@ -6567,19 +6561,19 @@
         <v>2</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>596</v>
+        <v>587</v>
       </c>
       <c r="D139" s="7" t="s">
         <v>150</v>
       </c>
       <c r="E139" s="7" t="s">
-        <v>597</v>
+        <v>588</v>
       </c>
       <c r="F139" s="7" t="s">
-        <v>598</v>
+        <v>589</v>
       </c>
       <c r="G139" s="7" t="s">
-        <v>599</v>
+        <v>590</v>
       </c>
       <c r="H139" s="7">
         <v>2</v>
@@ -6593,19 +6587,19 @@
         <v>2</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>600</v>
+        <v>591</v>
       </c>
       <c r="D140" s="7" t="s">
-        <v>601</v>
+        <v>592</v>
       </c>
       <c r="E140" s="7" t="s">
-        <v>602</v>
+        <v>593</v>
       </c>
       <c r="F140" s="7" t="s">
-        <v>603</v>
+        <v>594</v>
       </c>
       <c r="G140" s="7" t="s">
-        <v>604</v>
+        <v>595</v>
       </c>
       <c r="H140" s="7">
         <v>2</v>
@@ -6619,19 +6613,19 @@
         <v>2</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>605</v>
+        <v>596</v>
       </c>
       <c r="D141" s="7" t="s">
-        <v>606</v>
+        <v>597</v>
       </c>
       <c r="E141" s="7" t="s">
-        <v>607</v>
+        <v>598</v>
       </c>
       <c r="F141" s="7" t="s">
-        <v>608</v>
+        <v>599</v>
       </c>
       <c r="G141" s="7" t="s">
-        <v>609</v>
+        <v>600</v>
       </c>
       <c r="H141" s="7">
         <v>2</v>
@@ -6645,19 +6639,19 @@
         <v>2</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="D142" s="7" t="s">
-        <v>611</v>
+        <v>602</v>
       </c>
       <c r="E142" s="7" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="F142" s="7" t="s">
-        <v>613</v>
+        <v>604</v>
       </c>
       <c r="G142" s="7" t="s">
-        <v>614</v>
+        <v>605</v>
       </c>
       <c r="H142" s="7">
         <v>3</v>
@@ -6671,19 +6665,19 @@
         <v>2</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>615</v>
+        <v>606</v>
       </c>
       <c r="D143" s="7" t="s">
-        <v>616</v>
+        <v>607</v>
       </c>
       <c r="E143" s="7" t="s">
-        <v>617</v>
+        <v>608</v>
       </c>
       <c r="F143" s="7" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="G143" s="7" t="s">
-        <v>619</v>
+        <v>610</v>
       </c>
       <c r="H143" s="7">
         <v>2</v>
@@ -6697,19 +6691,19 @@
         <v>2</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>620</v>
+        <v>611</v>
       </c>
       <c r="D144" s="7" t="s">
-        <v>531</v>
+        <v>522</v>
       </c>
       <c r="E144" s="7" t="s">
         <v>95</v>
       </c>
       <c r="F144" s="7" t="s">
-        <v>568</v>
+        <v>559</v>
       </c>
       <c r="G144" s="7" t="s">
-        <v>621</v>
+        <v>612</v>
       </c>
       <c r="H144" s="7">
         <v>3</v>
@@ -6723,19 +6717,19 @@
         <v>2</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="D145" s="7" t="s">
-        <v>623</v>
+        <v>614</v>
       </c>
       <c r="E145" s="7" t="s">
-        <v>624</v>
+        <v>615</v>
       </c>
       <c r="F145" s="7" t="s">
-        <v>625</v>
+        <v>616</v>
       </c>
       <c r="G145" s="7" t="s">
-        <v>626</v>
+        <v>617</v>
       </c>
       <c r="H145" s="7">
         <v>2</v>
@@ -6749,19 +6743,19 @@
         <v>2</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>627</v>
+        <v>618</v>
       </c>
       <c r="D146" s="7" t="s">
-        <v>628</v>
+        <v>619</v>
       </c>
       <c r="E146" s="7" t="s">
-        <v>629</v>
+        <v>620</v>
       </c>
       <c r="F146" s="7" t="s">
-        <v>630</v>
+        <v>621</v>
       </c>
       <c r="G146" s="7" t="s">
-        <v>631</v>
+        <v>622</v>
       </c>
       <c r="H146" s="7">
         <v>3</v>
@@ -6775,19 +6769,19 @@
         <v>2</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>632</v>
+        <v>623</v>
       </c>
       <c r="D147" s="7" t="s">
-        <v>633</v>
+        <v>624</v>
       </c>
       <c r="E147" s="7" t="s">
-        <v>634</v>
+        <v>625</v>
       </c>
       <c r="F147" s="7" t="s">
-        <v>635</v>
+        <v>626</v>
       </c>
       <c r="G147" s="7" t="s">
-        <v>636</v>
+        <v>627</v>
       </c>
       <c r="H147" s="7">
         <v>3</v>
@@ -6801,19 +6795,19 @@
         <v>2</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>637</v>
+        <v>628</v>
       </c>
       <c r="D148" s="7" t="s">
-        <v>638</v>
+        <v>629</v>
       </c>
       <c r="E148" s="7" t="s">
-        <v>639</v>
+        <v>630</v>
       </c>
       <c r="F148" s="7" t="s">
-        <v>640</v>
+        <v>631</v>
       </c>
       <c r="G148" s="7" t="s">
-        <v>641</v>
+        <v>632</v>
       </c>
       <c r="H148" s="7">
         <v>2</v>
@@ -6827,22 +6821,22 @@
         <v>2</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>642</v>
+        <v>633</v>
       </c>
       <c r="D149" s="7" t="s">
-        <v>643</v>
+        <v>180</v>
       </c>
       <c r="E149" s="7" t="s">
-        <v>644</v>
+        <v>634</v>
       </c>
       <c r="F149" s="7" t="s">
-        <v>645</v>
+        <v>179</v>
       </c>
       <c r="G149" s="7" t="s">
-        <v>646</v>
+        <v>181</v>
       </c>
       <c r="H149" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.15">
@@ -6853,19 +6847,19 @@
         <v>2</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>647</v>
+        <v>635</v>
       </c>
       <c r="D150" s="7" t="s">
-        <v>180</v>
+        <v>537</v>
       </c>
       <c r="E150" s="7" t="s">
-        <v>648</v>
+        <v>87</v>
       </c>
       <c r="F150" s="7" t="s">
-        <v>179</v>
+        <v>636</v>
       </c>
       <c r="G150" s="7" t="s">
-        <v>181</v>
+        <v>88</v>
       </c>
       <c r="H150" s="7">
         <v>3</v>
@@ -6879,22 +6873,22 @@
         <v>2</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>649</v>
+        <v>637</v>
       </c>
       <c r="D151" s="7" t="s">
-        <v>546</v>
+        <v>638</v>
       </c>
       <c r="E151" s="7" t="s">
-        <v>87</v>
+        <v>639</v>
       </c>
       <c r="F151" s="7" t="s">
-        <v>650</v>
+        <v>640</v>
       </c>
       <c r="G151" s="7" t="s">
-        <v>88</v>
+        <v>641</v>
       </c>
       <c r="H151" s="7">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.15">
@@ -6905,22 +6899,22 @@
         <v>2</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>651</v>
+        <v>642</v>
       </c>
       <c r="D152" s="7" t="s">
-        <v>652</v>
+        <v>643</v>
       </c>
       <c r="E152" s="7" t="s">
-        <v>653</v>
+        <v>644</v>
       </c>
       <c r="F152" s="7" t="s">
-        <v>654</v>
+        <v>645</v>
       </c>
       <c r="G152" s="7" t="s">
-        <v>655</v>
+        <v>646</v>
       </c>
       <c r="H152" s="7">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.15">
@@ -6931,22 +6925,22 @@
         <v>2</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>656</v>
+        <v>647</v>
       </c>
       <c r="D153" s="7" t="s">
-        <v>657</v>
+        <v>648</v>
       </c>
       <c r="E153" s="7" t="s">
-        <v>658</v>
+        <v>649</v>
       </c>
       <c r="F153" s="7" t="s">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="G153" s="7" t="s">
-        <v>660</v>
+        <v>651</v>
       </c>
       <c r="H153" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.15">
@@ -6957,22 +6951,22 @@
         <v>2</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>661</v>
+        <v>652</v>
       </c>
       <c r="D154" s="7" t="s">
-        <v>662</v>
+        <v>653</v>
       </c>
       <c r="E154" s="7" t="s">
-        <v>663</v>
+        <v>654</v>
       </c>
       <c r="F154" s="7" t="s">
-        <v>664</v>
+        <v>655</v>
       </c>
       <c r="G154" s="7" t="s">
-        <v>665</v>
+        <v>656</v>
       </c>
       <c r="H154" s="7">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.15">
@@ -6983,22 +6977,22 @@
         <v>2</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>666</v>
+        <v>657</v>
       </c>
       <c r="D155" s="7" t="s">
-        <v>667</v>
+        <v>658</v>
       </c>
       <c r="E155" s="7" t="s">
-        <v>668</v>
+        <v>659</v>
       </c>
       <c r="F155" s="7" t="s">
-        <v>669</v>
+        <v>153</v>
       </c>
       <c r="G155" s="7" t="s">
-        <v>670</v>
+        <v>660</v>
       </c>
       <c r="H155" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.15">
@@ -7009,22 +7003,22 @@
         <v>2</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>671</v>
+        <v>661</v>
       </c>
       <c r="D156" s="7" t="s">
-        <v>672</v>
+        <v>389</v>
       </c>
       <c r="E156" s="7" t="s">
-        <v>673</v>
+        <v>662</v>
       </c>
       <c r="F156" s="7" t="s">
-        <v>153</v>
+        <v>392</v>
       </c>
       <c r="G156" s="7" t="s">
-        <v>674</v>
+        <v>663</v>
       </c>
       <c r="H156" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.15">
@@ -7035,22 +7029,22 @@
         <v>2</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>675</v>
+        <v>664</v>
       </c>
       <c r="D157" s="7" t="s">
-        <v>393</v>
+        <v>665</v>
       </c>
       <c r="E157" s="7" t="s">
-        <v>676</v>
+        <v>666</v>
       </c>
       <c r="F157" s="7" t="s">
-        <v>396</v>
+        <v>667</v>
       </c>
       <c r="G157" s="7" t="s">
-        <v>677</v>
+        <v>668</v>
       </c>
       <c r="H157" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.15">
@@ -7061,19 +7055,19 @@
         <v>2</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>678</v>
+        <v>669</v>
       </c>
       <c r="D158" s="7" t="s">
-        <v>679</v>
+        <v>670</v>
       </c>
       <c r="E158" s="7" t="s">
-        <v>680</v>
+        <v>671</v>
       </c>
       <c r="F158" s="7" t="s">
-        <v>681</v>
+        <v>672</v>
       </c>
       <c r="G158" s="7" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="H158" s="7">
         <v>3</v>
@@ -7087,22 +7081,22 @@
         <v>2</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>683</v>
+        <v>674</v>
       </c>
       <c r="D159" s="7" t="s">
-        <v>684</v>
+        <v>675</v>
       </c>
       <c r="E159" s="7" t="s">
-        <v>685</v>
+        <v>676</v>
       </c>
       <c r="F159" s="7" t="s">
-        <v>686</v>
+        <v>677</v>
       </c>
       <c r="G159" s="7" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="H159" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.15">
@@ -7113,19 +7107,19 @@
         <v>2</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>688</v>
+        <v>679</v>
       </c>
       <c r="D160" s="7" t="s">
-        <v>689</v>
+        <v>680</v>
       </c>
       <c r="E160" s="7" t="s">
-        <v>690</v>
+        <v>681</v>
       </c>
       <c r="F160" s="7" t="s">
-        <v>691</v>
+        <v>682</v>
       </c>
       <c r="G160" s="7" t="s">
-        <v>692</v>
+        <v>683</v>
       </c>
       <c r="H160" s="7">
         <v>2</v>
@@ -7139,22 +7133,22 @@
         <v>2</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>693</v>
+        <v>684</v>
       </c>
       <c r="D161" s="7" t="s">
-        <v>694</v>
+        <v>685</v>
       </c>
       <c r="E161" s="7" t="s">
-        <v>695</v>
+        <v>686</v>
       </c>
       <c r="F161" s="7" t="s">
-        <v>696</v>
+        <v>687</v>
       </c>
       <c r="G161" s="7" t="s">
-        <v>697</v>
+        <v>688</v>
       </c>
       <c r="H161" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.15">
@@ -7165,19 +7159,19 @@
         <v>2</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>698</v>
+        <v>689</v>
       </c>
       <c r="D162" s="7" t="s">
-        <v>699</v>
+        <v>690</v>
       </c>
       <c r="E162" s="7" t="s">
-        <v>700</v>
+        <v>691</v>
       </c>
       <c r="F162" s="7" t="s">
-        <v>701</v>
+        <v>692</v>
       </c>
       <c r="G162" s="7" t="s">
-        <v>702</v>
+        <v>693</v>
       </c>
       <c r="H162" s="7">
         <v>3</v>
@@ -7191,22 +7185,22 @@
         <v>2</v>
       </c>
       <c r="C163" s="4" t="s">
-        <v>703</v>
+        <v>694</v>
       </c>
       <c r="D163" s="7" t="s">
-        <v>704</v>
+        <v>155</v>
       </c>
       <c r="E163" s="7" t="s">
-        <v>705</v>
+        <v>176</v>
       </c>
       <c r="F163" s="7" t="s">
-        <v>706</v>
+        <v>695</v>
       </c>
       <c r="G163" s="7" t="s">
-        <v>707</v>
+        <v>696</v>
       </c>
       <c r="H163" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.15">
@@ -7217,22 +7211,22 @@
         <v>2</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>708</v>
+        <v>697</v>
       </c>
       <c r="D164" s="7" t="s">
-        <v>155</v>
+        <v>698</v>
       </c>
       <c r="E164" s="7" t="s">
-        <v>176</v>
+        <v>699</v>
       </c>
       <c r="F164" s="7" t="s">
-        <v>709</v>
+        <v>329</v>
       </c>
       <c r="G164" s="7" t="s">
-        <v>710</v>
+        <v>700</v>
       </c>
       <c r="H164" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.15">
@@ -7243,19 +7237,19 @@
         <v>2</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>711</v>
+        <v>701</v>
       </c>
       <c r="D165" s="7" t="s">
-        <v>712</v>
+        <v>702</v>
       </c>
       <c r="E165" s="7" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="F165" s="7" t="s">
-        <v>333</v>
+        <v>704</v>
       </c>
       <c r="G165" s="7" t="s">
-        <v>714</v>
+        <v>705</v>
       </c>
       <c r="H165" s="7">
         <v>2</v>
@@ -7269,22 +7263,22 @@
         <v>2</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>715</v>
+        <v>706</v>
       </c>
       <c r="D166" s="7" t="s">
-        <v>716</v>
+        <v>707</v>
       </c>
       <c r="E166" s="7" t="s">
-        <v>717</v>
+        <v>708</v>
       </c>
       <c r="F166" s="7" t="s">
-        <v>718</v>
+        <v>709</v>
       </c>
       <c r="G166" s="7" t="s">
-        <v>719</v>
+        <v>710</v>
       </c>
       <c r="H166" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.15">
@@ -7295,19 +7289,19 @@
         <v>2</v>
       </c>
       <c r="C167" s="4" t="s">
-        <v>720</v>
+        <v>711</v>
       </c>
       <c r="D167" s="7" t="s">
-        <v>721</v>
+        <v>384</v>
       </c>
       <c r="E167" s="7" t="s">
-        <v>722</v>
+        <v>712</v>
       </c>
       <c r="F167" s="7" t="s">
-        <v>723</v>
+        <v>713</v>
       </c>
       <c r="G167" s="7" t="s">
-        <v>724</v>
+        <v>705</v>
       </c>
       <c r="H167" s="7">
         <v>3</v>
@@ -7321,19 +7315,19 @@
         <v>2</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>725</v>
+        <v>714</v>
       </c>
       <c r="D168" s="7" t="s">
-        <v>388</v>
+        <v>715</v>
       </c>
       <c r="E168" s="7" t="s">
-        <v>726</v>
+        <v>716</v>
       </c>
       <c r="F168" s="7" t="s">
-        <v>727</v>
+        <v>717</v>
       </c>
       <c r="G168" s="7" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H168" s="7">
         <v>3</v>
@@ -7347,19 +7341,19 @@
         <v>2</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>728</v>
+        <v>719</v>
       </c>
       <c r="D169" s="7" t="s">
-        <v>729</v>
+        <v>720</v>
       </c>
       <c r="E169" s="7" t="s">
-        <v>730</v>
+        <v>721</v>
       </c>
       <c r="F169" s="7" t="s">
-        <v>731</v>
+        <v>403</v>
       </c>
       <c r="G169" s="7" t="s">
-        <v>732</v>
+        <v>722</v>
       </c>
       <c r="H169" s="7">
         <v>3</v>
@@ -7373,22 +7367,22 @@
         <v>2</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>733</v>
+        <v>723</v>
       </c>
       <c r="D170" s="7" t="s">
-        <v>734</v>
+        <v>724</v>
       </c>
       <c r="E170" s="7" t="s">
-        <v>735</v>
+        <v>725</v>
       </c>
       <c r="F170" s="7" t="s">
-        <v>407</v>
+        <v>726</v>
       </c>
       <c r="G170" s="7" t="s">
-        <v>736</v>
+        <v>727</v>
       </c>
       <c r="H170" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.15">
@@ -7399,22 +7393,22 @@
         <v>2</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>737</v>
+        <v>728</v>
       </c>
       <c r="D171" s="7" t="s">
-        <v>738</v>
+        <v>729</v>
       </c>
       <c r="E171" s="7" t="s">
-        <v>739</v>
+        <v>730</v>
       </c>
       <c r="F171" s="7" t="s">
-        <v>740</v>
+        <v>731</v>
       </c>
       <c r="G171" s="7" t="s">
-        <v>741</v>
+        <v>732</v>
       </c>
       <c r="H171" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.15">
@@ -7425,22 +7419,22 @@
         <v>2</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>742</v>
+        <v>733</v>
       </c>
       <c r="D172" s="7" t="s">
-        <v>743</v>
+        <v>734</v>
       </c>
       <c r="E172" s="7" t="s">
-        <v>744</v>
+        <v>735</v>
       </c>
       <c r="F172" s="7" t="s">
-        <v>745</v>
+        <v>736</v>
       </c>
       <c r="G172" s="7" t="s">
-        <v>746</v>
+        <v>737</v>
       </c>
       <c r="H172" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.15">
@@ -7451,22 +7445,22 @@
         <v>2</v>
       </c>
       <c r="C173" s="4" t="s">
-        <v>747</v>
+        <v>738</v>
       </c>
       <c r="D173" s="7" t="s">
-        <v>748</v>
+        <v>739</v>
       </c>
       <c r="E173" s="7" t="s">
-        <v>749</v>
+        <v>740</v>
       </c>
       <c r="F173" s="7" t="s">
-        <v>750</v>
+        <v>741</v>
       </c>
       <c r="G173" s="7" t="s">
-        <v>751</v>
+        <v>742</v>
       </c>
       <c r="H173" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.15">
@@ -7477,22 +7471,22 @@
         <v>2</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>752</v>
+        <v>743</v>
       </c>
       <c r="D174" s="7" t="s">
-        <v>753</v>
+        <v>744</v>
       </c>
       <c r="E174" s="7" t="s">
-        <v>754</v>
+        <v>745</v>
       </c>
       <c r="F174" s="7" t="s">
-        <v>755</v>
+        <v>746</v>
       </c>
       <c r="G174" s="7" t="s">
-        <v>756</v>
+        <v>747</v>
       </c>
       <c r="H174" s="7">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.15">
@@ -7503,22 +7497,22 @@
         <v>2</v>
       </c>
       <c r="C175" s="4" t="s">
-        <v>757</v>
+        <v>748</v>
       </c>
       <c r="D175" s="7" t="s">
-        <v>758</v>
+        <v>749</v>
       </c>
       <c r="E175" s="7" t="s">
-        <v>759</v>
+        <v>750</v>
       </c>
       <c r="F175" s="7" t="s">
-        <v>760</v>
+        <v>751</v>
       </c>
       <c r="G175" s="7" t="s">
-        <v>761</v>
+        <v>752</v>
       </c>
       <c r="H175" s="7">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.15">
@@ -7529,19 +7523,19 @@
         <v>2</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>762</v>
+        <v>753</v>
       </c>
       <c r="D176" s="7" t="s">
-        <v>763</v>
+        <v>754</v>
       </c>
       <c r="E176" s="7" t="s">
-        <v>764</v>
+        <v>755</v>
       </c>
       <c r="F176" s="7" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
       <c r="G176" s="7" t="s">
-        <v>766</v>
+        <v>757</v>
       </c>
       <c r="H176" s="7">
         <v>3</v>
@@ -7555,19 +7549,19 @@
         <v>2</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>767</v>
+        <v>758</v>
       </c>
       <c r="D177" s="7" t="s">
-        <v>768</v>
+        <v>759</v>
       </c>
       <c r="E177" s="7" t="s">
-        <v>769</v>
+        <v>760</v>
       </c>
       <c r="F177" s="7" t="s">
-        <v>770</v>
+        <v>761</v>
       </c>
       <c r="G177" s="7" t="s">
-        <v>771</v>
+        <v>762</v>
       </c>
       <c r="H177" s="7">
         <v>3</v>
@@ -7581,22 +7575,22 @@
         <v>2</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>772</v>
+        <v>763</v>
       </c>
       <c r="D178" s="7" t="s">
-        <v>773</v>
+        <v>764</v>
       </c>
       <c r="E178" s="7" t="s">
-        <v>774</v>
+        <v>765</v>
       </c>
       <c r="F178" s="7" t="s">
-        <v>775</v>
+        <v>766</v>
       </c>
       <c r="G178" s="7" t="s">
-        <v>776</v>
+        <v>767</v>
       </c>
       <c r="H178" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.15">
@@ -7607,22 +7601,22 @@
         <v>2</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>777</v>
+        <v>768</v>
       </c>
       <c r="D179" s="7" t="s">
-        <v>778</v>
+        <v>769</v>
       </c>
       <c r="E179" s="7" t="s">
-        <v>779</v>
+        <v>770</v>
       </c>
       <c r="F179" s="7" t="s">
-        <v>780</v>
+        <v>771</v>
       </c>
       <c r="G179" s="7" t="s">
-        <v>781</v>
+        <v>772</v>
       </c>
       <c r="H179" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.15">
@@ -7633,22 +7627,22 @@
         <v>2</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>782</v>
+        <v>773</v>
       </c>
       <c r="D180" s="7" t="s">
-        <v>783</v>
+        <v>774</v>
       </c>
       <c r="E180" s="7" t="s">
-        <v>784</v>
+        <v>775</v>
       </c>
       <c r="F180" s="7" t="s">
-        <v>785</v>
+        <v>776</v>
       </c>
       <c r="G180" s="7" t="s">
-        <v>786</v>
+        <v>777</v>
       </c>
       <c r="H180" s="7">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.15">
@@ -7659,22 +7653,22 @@
         <v>2</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>787</v>
+        <v>778</v>
       </c>
       <c r="D181" s="7" t="s">
-        <v>788</v>
+        <v>779</v>
       </c>
       <c r="E181" s="7" t="s">
-        <v>789</v>
+        <v>780</v>
       </c>
       <c r="F181" s="7" t="s">
-        <v>790</v>
+        <v>781</v>
       </c>
       <c r="G181" s="7" t="s">
-        <v>791</v>
+        <v>749</v>
       </c>
       <c r="H181" s="7">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.15">
@@ -7685,19 +7679,19 @@
         <v>2</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>792</v>
+        <v>782</v>
       </c>
       <c r="D182" s="7" t="s">
-        <v>793</v>
+        <v>783</v>
       </c>
       <c r="E182" s="7" t="s">
-        <v>794</v>
+        <v>784</v>
       </c>
       <c r="F182" s="7" t="s">
-        <v>795</v>
+        <v>785</v>
       </c>
       <c r="G182" s="7" t="s">
-        <v>763</v>
+        <v>786</v>
       </c>
       <c r="H182" s="7">
         <v>3</v>
@@ -7711,22 +7705,22 @@
         <v>2</v>
       </c>
       <c r="C183" s="4" t="s">
-        <v>796</v>
+        <v>787</v>
       </c>
       <c r="D183" s="7" t="s">
-        <v>797</v>
+        <v>788</v>
       </c>
       <c r="E183" s="7" t="s">
-        <v>798</v>
+        <v>789</v>
       </c>
       <c r="F183" s="7" t="s">
-        <v>799</v>
+        <v>790</v>
       </c>
       <c r="G183" s="7" t="s">
-        <v>800</v>
+        <v>791</v>
       </c>
       <c r="H183" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.15">
@@ -7737,22 +7731,22 @@
         <v>2</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>801</v>
+        <v>792</v>
       </c>
       <c r="D184" s="7" t="s">
-        <v>802</v>
+        <v>793</v>
       </c>
       <c r="E184" s="7" t="s">
-        <v>803</v>
+        <v>794</v>
       </c>
       <c r="F184" s="7" t="s">
-        <v>804</v>
+        <v>795</v>
       </c>
       <c r="G184" s="7" t="s">
-        <v>805</v>
+        <v>796</v>
       </c>
       <c r="H184" s="7">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.15">
@@ -7763,19 +7757,19 @@
         <v>2</v>
       </c>
       <c r="C185" s="4" t="s">
-        <v>806</v>
+        <v>797</v>
       </c>
       <c r="D185" s="7" t="s">
-        <v>807</v>
+        <v>214</v>
       </c>
       <c r="E185" s="7" t="s">
-        <v>808</v>
+        <v>215</v>
       </c>
       <c r="F185" s="7" t="s">
-        <v>809</v>
+        <v>216</v>
       </c>
       <c r="G185" s="7" t="s">
-        <v>810</v>
+        <v>798</v>
       </c>
       <c r="H185" s="7">
         <v>4</v>
@@ -7789,22 +7783,22 @@
         <v>2</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>811</v>
+        <v>799</v>
       </c>
       <c r="D186" s="7" t="s">
-        <v>214</v>
+        <v>800</v>
       </c>
       <c r="E186" s="7" t="s">
-        <v>215</v>
+        <v>801</v>
       </c>
       <c r="F186" s="7" t="s">
-        <v>216</v>
+        <v>802</v>
       </c>
       <c r="G186" s="7" t="s">
-        <v>812</v>
+        <v>803</v>
       </c>
       <c r="H186" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.15">
@@ -7815,22 +7809,22 @@
         <v>2</v>
       </c>
       <c r="C187" s="4" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="D187" s="7" t="s">
-        <v>814</v>
+        <v>805</v>
       </c>
       <c r="E187" s="7" t="s">
-        <v>815</v>
+        <v>806</v>
       </c>
       <c r="F187" s="7" t="s">
-        <v>816</v>
+        <v>807</v>
       </c>
       <c r="G187" s="7" t="s">
-        <v>817</v>
+        <v>808</v>
       </c>
       <c r="H187" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.15">
@@ -7841,47 +7835,21 @@
         <v>2</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>818</v>
+        <v>809</v>
       </c>
       <c r="D188" s="7" t="s">
-        <v>819</v>
+        <v>810</v>
       </c>
       <c r="E188" s="7" t="s">
-        <v>820</v>
+        <v>811</v>
       </c>
       <c r="F188" s="7" t="s">
-        <v>821</v>
+        <v>812</v>
       </c>
       <c r="G188" s="7" t="s">
-        <v>822</v>
+        <v>813</v>
       </c>
       <c r="H188" s="7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A189" s="8">
-        <v>2096</v>
-      </c>
-      <c r="B189" s="8">
-        <v>2</v>
-      </c>
-      <c r="C189" s="4" t="s">
-        <v>823</v>
-      </c>
-      <c r="D189" s="7" t="s">
-        <v>824</v>
-      </c>
-      <c r="E189" s="7" t="s">
-        <v>825</v>
-      </c>
-      <c r="F189" s="7" t="s">
-        <v>826</v>
-      </c>
-      <c r="G189" s="7" t="s">
-        <v>827</v>
-      </c>
-      <c r="H189" s="7">
         <v>3</v>
       </c>
     </row>
